--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Confirm pricing v2 numbers (Başlangıç / Büyüme / Pro / Kurumsal, Aylık, modules)</t>
+          <t>Confirm pricing v2 package prices (Başlangıç / Büyüme / Pro / Kurumsal, Aylık)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1945,7 +1945,7 @@
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Model decided 19 Oct; numbers are a proposal</t>
+          <t>Confirmed 19 Oct 19:48 via command board</t>
         </is>
       </c>
       <c r="J9" s="4">
@@ -1956,12 +1956,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T05b</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Take the 4 accountant questions (seller of record + KDV, partner payout paperwork, deductibility)</t>
+          <t>Confirm pricing v2 module prices (finance, arbitrage, photo studio, extra store/orders)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>pricing-v2 §5. Decides iyzico/PayTR entity</t>
+          <t>Still a proposal</t>
         </is>
       </c>
       <c r="J10" s="4">
@@ -2001,25 +2001,25 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Accountant answers the 4 questions</t>
+          <t>Take the 4 accountant questions (seller of record + KDV, partner payout paperwork, deductibility)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Accountant</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2032,12 +2032,12 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>pricing-v2 §5. Decides iyzico/PayTR entity</t>
+        </is>
+      </c>
       <c r="J11" s="4">
         <f>IF(AND(D11&lt;&gt;"",D11&lt;TODAY(),E11&lt;&gt;"Done",E11&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2046,40 +2046,40 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>OK to switch the tutorials Unlisted → Public</t>
+          <t>Accountant answers the 4 questions</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Accountant</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>46328</v>
+        <v>46333</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr"/>
@@ -2091,12 +2091,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Create the Stripe partner coupon(s) and set STRIPE_PARTNER_COUPON_ID via stdin</t>
+          <t>OK to switch the tutorials Unlisted → Public</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2114,20 +2114,20 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com/coupons</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>20% once on yearly / repeating 3 months on Aylık</t>
-        </is>
-      </c>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="4">
         <f>IF(AND(D13&lt;&gt;"",D13&lt;TODAY(),E13&lt;&gt;"Done",E13&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2136,12 +2136,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Create GTM container + GA4 + Meta pixel IDs and set them in the Hetzner .env</t>
+          <t>Create the Stripe partner coupon(s) and set STRIPE_PARTNER_COUPON_ID via stdin</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>46356</v>
+        <v>46328</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -2164,13 +2164,13 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/tracking/README.md</t>
+          <t>https://dashboard.stripe.com/coupons</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 gate</t>
+          <t>20% once on yearly / repeating 3 months on Aylık</t>
         </is>
       </c>
       <c r="J14" s="4">
@@ -2181,12 +2181,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Enable Stripe Global Payouts on the Tamsar, Inc. account</t>
+          <t>Create GTM container + GA4 + Meta pixel IDs and set them in the Hetzner .env</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>46376</v>
+        <v>46356</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2204,22 +2204,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/tracking/README.md</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Before the first payout run (5 Jan)</t>
+          <t>Phase 2 gate</t>
         </is>
       </c>
       <c r="J15" s="4">
@@ -2230,12 +2226,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Follow up Hepsiburada integrator ticket 1-404875606841365</t>
+          <t>Enable Stripe Global Payouts on the Tamsar, Inc. account</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2244,11 +2240,11 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>46316</v>
+        <v>46376</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2256,11 +2252,19 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>https://dashboard.stripe.com</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Planned close 21 Oct (Satıcı Paneli › Destek Kayıtlarım)</t>
+          <t>Before the first payout run (5 Jan)</t>
         </is>
       </c>
       <c r="J16" s="4">
@@ -2271,41 +2275,37 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Hire a Bionluk freelancer for list-building (120 groups + 60 X/YouTube)</t>
+          <t>Follow up Hepsiburada integrator ticket 1-404875606841365</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Budget ₺4–6k; brief in gameplan §4.4</t>
+          <t>Planned close 21 Oct (Satıcı Paneli › Destek Kayıtlarım)</t>
         </is>
       </c>
       <c r="J17" s="4">
@@ -2316,12 +2316,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Shortlist + score 110 FB/Telegram groups and 20 müşavirler in Partner pipeline</t>
+          <t>Hire a Bionluk freelancer for list-building (120 groups + 60 X/YouTube)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -2342,15 +2342,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Scoring rubric: gameplan §4.4</t>
+          <t>Budget ₺4–6k; brief in gameplan §4.4</t>
         </is>
       </c>
       <c r="J18" s="4">
@@ -2361,17 +2361,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Shortlist + score 50 X accounts and 20 YouTube channels in Partner pipeline</t>
+          <t>Shortlist + score 110 FB/Telegram groups and 20 müşavirler in Partner pipeline</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -2388,8 +2388,16 @@
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Scoring rubric: gameplan §4.4</t>
+        </is>
+      </c>
       <c r="J19" s="4">
         <f>IF(AND(D19&lt;&gt;"",D19&lt;TODAY(),E19&lt;&gt;"Done",E19&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2398,17 +2406,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Week 1: 15 helpful answers in target groups (no links)</t>
+          <t>Shortlist + score 50 X accounts and 20 YouTube channels in Partner pipeline</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -2421,7 +2429,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -2435,17 +2443,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Week 1: 15 helpful X replies on e-ihracat threads</t>
+          <t>Week 1: 15 helpful answers in target groups (no links)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2472,21 +2480,21 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Manual prod check of referral Stage A: open /?ref=TEST-PARTNER, sign up, see 1 signup in /admin/partners, then delete test data</t>
+          <t>Week 1: 15 helpful X replies on e-ihracat threads</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2495,20 +2503,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>https://kolayxport.com/admin/partners</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>With Claude d7; see Tests Q01</t>
-        </is>
-      </c>
+      <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="4">
         <f>IF(AND(D22&lt;&gt;"",D22&lt;TODAY(),E22&lt;&gt;"Done",E22&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2517,12 +2517,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Send the first partner messages (Varyant 5 / 6)</t>
+          <t>Manual prod check of referral Stage A: open /?ref=TEST-PARTNER, sign up, see 1 signup in /admin/partners, then delete test data</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>46328</v>
+        <v>46319</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -2545,17 +2545,13 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>T09, T18</t>
-        </is>
-      </c>
+          <t>https://kolayxport.com/admin/partners</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Only after tracking is confirmed</t>
+          <t>With Claude d7; see Tests Q01</t>
         </is>
       </c>
       <c r="J23" s="4">
@@ -2566,12 +2562,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Fact-check the blog posts (2 a week)</t>
+          <t>Send the first partner messages (Varyant 5 / 6)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2580,7 +2576,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -2589,18 +2585,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>T09, T18</t>
+        </is>
+      </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Recurring every Tue/Thu</t>
+          <t>Only after tracking is confirmed</t>
         </is>
       </c>
       <c r="J24" s="4">
@@ -2611,12 +2611,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>First live demo in a partner group (scripted, 30 min)</t>
+          <t>Fact-check the blog posts (2 a week)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46344</v>
+        <v>46329</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -2637,9 +2637,17 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Recurring every Tue/Thu</t>
+        </is>
+      </c>
       <c r="J25" s="4">
         <f>IF(AND(D25&lt;&gt;"",D25&lt;TODAY(),E25&lt;&gt;"Done",E25&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2648,12 +2656,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Ask the first paying customers for written testimonial consent</t>
+          <t>First live demo in a partner group (scripted, 30 min)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2662,7 +2670,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46365</v>
+        <v>46344</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -2671,14 +2679,10 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="4">
@@ -2689,21 +2693,21 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Phase 2: start Instagram organic (only if the gate passed)</t>
+          <t>Ask the first paying customers for written testimonial consent</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>46398</v>
+        <v>46365</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -2717,14 +2721,10 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="4">
         <f>IF(AND(D27&lt;&gt;"",D27&lt;TODAY(),E27&lt;&gt;"Done",E27&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -2734,43 +2734,43 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage A (capture, claim, admin report)</t>
+          <t>Phase 2: start Instagram organic (only if the gate passed)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>46314</v>
+        <v>46398</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Deployed b6ee9895</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="4">
         <f>IF(AND(D28&lt;&gt;"",D28&lt;TODAY(),E28&lt;&gt;"Done",E28&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2779,12 +2779,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T25</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
+          <t>Referral Stage A (capture, claim, admin report)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2793,11 +2793,11 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>46333</v>
+        <v>46314</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2810,14 +2810,10 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Spec §3–6</t>
+          <t>Deployed b6ee9895</t>
         </is>
       </c>
       <c r="J29" s="4">
@@ -2828,25 +2824,25 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>T26</t>
+          <t>T25</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
+          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Claude: to assign</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>46341</v>
+        <v>46333</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2856,15 +2852,19 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>T05</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr"/>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Spec §3–6</t>
+        </is>
+      </c>
       <c r="J30" s="4">
         <f>IF(AND(D30&lt;&gt;"",D30&lt;TODAY(),E30&lt;&gt;"Done",E30&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2873,12 +2873,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>T26</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P2: iyzico/PayTR yearly checkout with taksit</t>
+          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2887,11 +2887,11 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>46356</v>
+        <v>46341</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2906,10 +2906,14 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr"/>
+          <t>T05b (modules only)</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Package prices decided; can start</t>
+        </is>
+      </c>
       <c r="J31" s="4">
         <f>IF(AND(D31&lt;&gt;"",D31&lt;TODAY(),E31&lt;&gt;"Done",E31&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2918,17 +2922,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>T28</t>
+          <t>T27</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P4: /fiyatlandirma redesign</t>
+          <t>Pricing v2 P2: iyzico/PayTR yearly checkout with taksit</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: to assign</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -2941,7 +2945,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2951,7 +2955,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>T05, T07</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr"/>
@@ -2963,12 +2967,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T29</t>
+          <t>T28</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Upload the remaining 8 tutorials</t>
+          <t>Pricing v2 P4: /fiyatlandirma redesign</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2977,11 +2981,11 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46315</v>
+        <v>46356</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2991,10 +2995,14 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>T05, T07</t>
+        </is>
+      </c>
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="4">
         <f>IF(AND(D33&lt;&gt;"",D33&lt;TODAY(),E33&lt;&gt;"Done",E33&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3004,12 +3012,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T29</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Blog cadence: 2 posts a week from the content calendar</t>
+          <t>Upload the remaining 8 tutorials</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3018,11 +3026,11 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>46329</v>
+        <v>46315</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3032,14 +3040,10 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="4">
         <f>IF(AND(D34&lt;&gt;"",D34&lt;TODAY(),E34&lt;&gt;"Done",E34&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3049,12 +3053,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
+          <t>Blog cadence: 2 posts a week from the content calendar</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3063,7 +3067,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -3077,12 +3081,12 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>T07, T25</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr"/>
@@ -3094,12 +3098,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T31</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Privacy notice: one line on masked referrals shown to partners</t>
+          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3122,30 +3126,60 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Lawyer-review flag</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>T07, T25</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="4">
         <f>IF(AND(D36&lt;&gt;"",D36&lt;TODAY(),E36&lt;&gt;"Done",E36&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="8" t="n"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Privacy notice: one line on masked referrals shown to partners</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Lawyer-review flag</t>
+        </is>
+      </c>
       <c r="J37" s="4">
         <f>IF(AND(D37&lt;&gt;"",D37&lt;TODAY(),E37&lt;&gt;"Done",E37&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -30203,7 +30237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30511,7 +30545,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Payments collected by Tamsar, Inc. (US) in TRY under its agreement with Modsons</t>
+          <t>Pricing v2 prices CONFIRMED: Başlangıç ₺29.990, Büyüme ₺54.990, Pro ₺89.990, Kurumsal from ₺149.990 a year; Aylık ₺2.999 a month; all +KDV. Module prices still a proposal; partners quote no prices until checkout exists</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -30521,12 +30555,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>pricing-v2 §1</t>
+          <t>command board 19 Oct 19:48 (via orchestrator)</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Proposal: Modsons sells to Turkish customers; open with the accountant</t>
+          <t>Seller of record / KDV still with the accountant</t>
         </is>
       </c>
     </row>
@@ -30536,27 +30570,45 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
+          <t>Payments collected by Tamsar, Inc. (US) in TRY under its agreement with Modsons</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>pricing-v2 §1</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Proposal: Modsons sells to Turkish customers; open with the accountant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
           <t>Cookie panel is live (since 2026-10-17); only tracking IDs gate Phase 2 measurement</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>gtm-overhaul (verified)</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>turkey-gameplan §4.9</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="E18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -30907,6 +30959,13 @@
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -2883,15 +2883,15 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Claude: to assign</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>46341</v>
+        <v>46314</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2904,14 +2904,10 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>T05b (modules only)</t>
-        </is>
-      </c>
+      <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Package prices decided; can start</t>
+          <t>Deployed d44c426e behind PRICING_V2 (flag off)</t>
         </is>
       </c>
       <c r="J31" s="4">
@@ -2922,35 +2918,35 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>T26b</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P2: iyzico/PayTR yearly checkout with taksit</t>
+          <t>Pricing v2 P3: Stripe prices for Aylık + modules</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Claude: to assign</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46356</v>
+        <v>46340</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+          <t>https://dashboard.stripe.com/products</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2958,7 +2954,11 @@
           <t>T07</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>On hold until the accountant answers (orchestrator decision)</t>
+        </is>
+      </c>
       <c r="J32" s="4">
         <f>IF(AND(D32&lt;&gt;"",D32&lt;TODAY(),E32&lt;&gt;"Done",E32&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2967,17 +2967,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T28</t>
+          <t>T27</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P4: /fiyatlandirma redesign</t>
+          <t>Pricing v2 P2: iyzico/PayTR yearly checkout with taksit</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: to assign</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>T05, T07</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr"/>
@@ -3012,12 +3012,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>T29</t>
+          <t>T28</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Upload the remaining 8 tutorials</t>
+          <t>Pricing v2 P4: /fiyatlandirma redesign</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3026,11 +3026,11 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>46315</v>
+        <v>46356</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3040,10 +3040,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>T05, T07</t>
+        </is>
+      </c>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="4">
         <f>IF(AND(D34&lt;&gt;"",D34&lt;TODAY(),E34&lt;&gt;"Done",E34&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3053,12 +3057,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T29</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Blog cadence: 2 posts a week from the content calendar</t>
+          <t>Upload the remaining 8 tutorials</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3067,11 +3071,11 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>46329</v>
+        <v>46315</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3081,14 +3085,10 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="4">
         <f>IF(AND(D35&lt;&gt;"",D35&lt;TODAY(),E35&lt;&gt;"Done",E35&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3098,12 +3098,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
+          <t>Blog cadence: 2 posts a week from the content calendar</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>T07, T25</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T31</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Privacy notice: one line on masked referrals shown to partners</t>
+          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3171,30 +3171,60 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Lawyer-review flag</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>T07, T25</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="4">
         <f>IF(AND(D37&lt;&gt;"",D37&lt;TODAY(),E37&lt;&gt;"Done",E37&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="8" t="n"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Privacy notice: one line on masked referrals shown to partners</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Lawyer-review flag</t>
+        </is>
+      </c>
       <c r="J38" s="4">
         <f>IF(AND(D38&lt;&gt;"",D38&lt;TODAY(),E38&lt;&gt;"Done",E38&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Confirm pricing v2 module prices (finance, arbitrage, photo studio, extra store/orders)</t>
+          <t>Final OK on module prices (finance ₺990, arbitrage ₺990, photo studio ₺790, extra store ₺490, +500 orders ₺490 a month)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1970,11 +1970,11 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Still a proposal</t>
+          <t>Already created in Stripe at these amounts by d7; on Atilla's board</t>
         </is>
       </c>
       <c r="J10" s="4">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Take the 4 accountant questions (seller of record + KDV, partner payout paperwork, deductibility)</t>
+          <t>Decide seller of record + KDV</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46326</v>
+        <v>46314</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>pricing-v2 §5. Decides iyzico/PayTR entity</t>
+          <t>Resolved by Atilla: Tamsar, Inc. sells, TRY via Stripe, no KDV added; Modsons invoices Tamsar</t>
         </is>
       </c>
       <c r="J11" s="4">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Accountant answers the 4 questions</t>
+          <t>Accountant: confirm partner payout paperwork once (W-8BEN; partners declare income in Turkey)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>46333</v>
+        <v>46376</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -2077,12 +2077,12 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Seller question resolved by Atilla (19 Oct); only this check remains, before the first payout (5 Jan)</t>
+        </is>
+      </c>
       <c r="J12" s="4">
         <f>IF(AND(D12&lt;&gt;"",D12&lt;TODAY(),E12&lt;&gt;"Done",E12&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2257,11 +2257,7 @@
           <t>https://dashboard.stripe.com</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
+      <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Before the first payout run (5 Jan)</t>
@@ -2923,20 +2919,20 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P3: Stripe prices for Aylık + modules</t>
+          <t>Pricing v2 P3: Stripe prices (all 14: yearly packages, Aylık, modules)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46340</v>
+        <v>46314</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2949,14 +2945,10 @@
           <t>https://dashboard.stripe.com/products</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
+      <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>On hold until the accountant answers (orchestrator decision)</t>
+          <t>Created live, inert behind PRICING_V2; code waiting for a deploy slot</t>
         </is>
       </c>
       <c r="J32" s="4">
@@ -2972,20 +2964,20 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P2: iyzico/PayTR yearly checkout with taksit</t>
+          <t>Approve taksit option: 'yearly, paid monthly on a 12-month commitment' via Stripe (iyzico/PayTR dropped: Turkish merchants only)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Claude: to assign</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46356</v>
+        <v>46321</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2998,12 +2990,12 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>pricing-v2 §5; then 3 more Stripe prices + commitment rule (dev)</t>
+        </is>
+      </c>
       <c r="J33" s="4">
         <f>IF(AND(D33&lt;&gt;"",D33&lt;TODAY(),E33&lt;&gt;"Done",E33&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3017,7 +3009,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P4: /fiyatlandirma redesign</t>
+          <t>Pricing v2 P4: /fiyatlandirma redesign (final amounts, no '+KDV')</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3030,7 +3022,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3045,7 +3037,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>T05, T07</t>
+          <t>T05b, T27</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr"/>
@@ -30267,7 +30259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30625,41 +30617,91 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
+          <t>Seller of record = Tamsar, Inc. for all customers; charges in TRY via Stripe with NO KDV added; prices are final amounts. Modsons invoices Tamsar for services and runs marketing in Turkey</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>d7 session (via orchestrator)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Supersedes '+KDV' and the Modsons-sells proposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>All 14 Stripe prices created (yearly packages, Aylık, modules), live but inert behind PRICING_V2</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Atilla / d7</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>orchestrator</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>iyzico/PayTR dropped (Turkish merchants only; Tamsar, Inc. sells). Taksit replacement proposed: yearly paid monthly on a 12-month commitment</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Plan (proposal)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>pricing-v2 §5</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Waiting for Atilla (T27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>Cookie panel is live (since 2026-10-17); only tracking IDs gate Phase 2 measurement</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>gtm-overhaul (verified)</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>turkey-gameplan §4.9</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
+      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -30996,6 +31038,27 @@
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Approve taksit option: 'yearly, paid monthly on a 12-month commitment' via Stripe (iyzico/PayTR dropped: Turkish merchants only)</t>
+          <t>Decide taksit option</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2973,11 +2973,11 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2993,7 +2993,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>pricing-v2 §5; then 3 more Stripe prices + commitment rule (dev)</t>
+          <t>Decided: yearly = pay-in-full only (Stripe card); Aylık = no-commitment option; iyzico/PayTR dropped. Parked: real taksit only via a Turkish seller entity later</t>
         </is>
       </c>
       <c r="J33" s="4">
@@ -30259,7 +30259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30688,27 +30688,45 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>Yearly packages are PAY-IN-FULL ONLY (Stripe card); no 'yearly, paid monthly'; Aylık ₺2.999 stays the no-commitment option; bounty stays 25% of the first yearly payment (no split); P2 iyzico/PayTR dropped</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>board (via orchestrator)</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Parked idea: real taksit only via a Turkish seller entity later</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>Cookie panel is live (since 2026-10-17); only tracking IDs gate Phase 2 measurement</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>gtm-overhaul (verified)</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>turkey-gameplan §4.9</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
+      <c r="E22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -31059,6 +31077,13 @@
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -1970,11 +1970,11 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>46319</v>
+        <v>46314</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Already created in Stripe at these amounts by d7; on Atilla's board</t>
+          <t>Confirmed 19 Oct 20:23 via board; yearly ×10; no KDV added</t>
         </is>
       </c>
       <c r="J10" s="4">
@@ -30259,7 +30259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30713,27 +30713,41 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
+          <t>Module prices CONFIRMED: Finans ₺990, Arbitraj ₺990, Toplu fotoğraf stüdyosu ₺790, Ek mağaza ₺490, +500 sipariş ₺490 a month; yearly ×10; final amounts, no KDV added</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>board 19 Oct 20:23 (via orchestrator)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>Cookie panel is live (since 2026-10-17); only tracking IDs gate Phase 2 measurement</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>gtm-overhaul (verified)</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>turkey-gameplan §4.9</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
+      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -31084,6 +31098,13 @@
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -2141,20 +2141,20 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Create the Stripe partner coupon(s) and set STRIPE_PARTNER_COUPON_ID via stdin</t>
+          <t>Partner coupon in Stripe + STRIPE_PARTNER_COUPON_ID</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2170,7 +2170,7 @@
       <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>20% once on yearly / repeating 3 months on Aylık</t>
+          <t>KX_PARTNER_20_3M: 20% repeating 3 months = 20% once on yearly, first 3 months on Aylık; in prod .env; never stacks with founding</t>
         </is>
       </c>
       <c r="J14" s="4">

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Create GTM container + GA4 + Meta pixel IDs and set them in the Hetzner .env</t>
+          <t>Tracking: GTM + GA4 created and published (GTM-N6SW5T7K, G-V4ZC6HS65N, account kolayxport@gmail.com). Remaining: put both IDs in the Hetzner .env + rebuild; mark sign_up/start_trial/purchase as GA4 key events after first data</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 gate</t>
+          <t>Claude set up GTM/GA4 on 19 Oct; .env write is blocked for Claude by permissions</t>
         </is>
       </c>
       <c r="J15" s="4">
@@ -2226,12 +2226,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T10b</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Enable Stripe Global Payouts on the Tamsar, Inc. account</t>
+          <t>Meta pixel + Conversions API token: log in to Meta Business (kolayxport) so it can be created; add the pixel tag in GTM</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>46376</v>
+        <v>46371</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -2249,18 +2249,18 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com</t>
+          <t>https://business.facebook.com/events_manager2</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Before the first payout run (5 Jan)</t>
+          <t>Phase 2 only (ads); Claude cannot enter the Facebook password</t>
         </is>
       </c>
       <c r="J16" s="4">
@@ -2271,12 +2271,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Follow up Hepsiburada integrator ticket 1-404875606841365</t>
+          <t>Enable Stripe Global Payouts on the Tamsar, Inc. account</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2285,11 +2285,11 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>46316</v>
+        <v>46376</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Waiting</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -2297,11 +2297,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>https://dashboard.stripe.com</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Planned close 21 Oct (Satıcı Paneli › Destek Kayıtlarım)</t>
+          <t>Before the first payout run (5 Jan)</t>
         </is>
       </c>
       <c r="J17" s="4">
@@ -2312,41 +2316,37 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Hire a Bionluk freelancer for list-building (120 groups + 60 X/YouTube)</t>
+          <t>Follow up Hepsiburada integrator ticket 1-404875606841365</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Waiting</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Budget ₺4–6k; brief in gameplan §4.4</t>
+          <t>Planned close 21 Oct (Satıcı Paneli › Destek Kayıtlarım)</t>
         </is>
       </c>
       <c r="J18" s="4">
@@ -2357,12 +2357,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Shortlist + score 110 FB/Telegram groups and 20 müşavirler in Partner pipeline</t>
+          <t>Hire a Bionluk freelancer for list-building (120 groups + 60 X/YouTube)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -2383,15 +2383,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Scoring rubric: gameplan §4.4</t>
+          <t>Budget ₺4–6k; brief in gameplan §4.4</t>
         </is>
       </c>
       <c r="J19" s="4">
@@ -2402,17 +2402,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Shortlist + score 50 X accounts and 20 YouTube channels in Partner pipeline</t>
+          <t>Shortlist + score 110 FB/Telegram groups and 20 müşavirler in Partner pipeline</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -2429,8 +2429,16 @@
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Scoring rubric: gameplan §4.4</t>
+        </is>
+      </c>
       <c r="J20" s="4">
         <f>IF(AND(D20&lt;&gt;"",D20&lt;TODAY(),E20&lt;&gt;"Done",E20&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2439,17 +2447,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Week 1: 15 helpful answers in target groups (no links)</t>
+          <t>Shortlist + score 50 X accounts and 20 YouTube channels in Partner pipeline</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -2462,7 +2470,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -2476,17 +2484,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Week 1: 15 helpful X replies on e-ihracat threads</t>
+          <t>Week 1: 15 helpful answers in target groups (no links)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -2513,21 +2521,21 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Manual prod check of referral Stage A: open /?ref=TEST-PARTNER, sign up, see 1 signup in /admin/partners, then delete test data</t>
+          <t>Week 1: 15 helpful X replies on e-ihracat threads</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -2536,20 +2544,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>https://kolayxport.com/admin/partners</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>With Claude d7; see Tests Q01</t>
-        </is>
-      </c>
+      <c r="I23" s="8" t="inlineStr"/>
       <c r="J23" s="4">
         <f>IF(AND(D23&lt;&gt;"",D23&lt;TODAY(),E23&lt;&gt;"Done",E23&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2558,12 +2558,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Send the first partner messages (Varyant 5 / 6)</t>
+          <t>Manual prod check of referral Stage A: open /?ref=TEST-PARTNER, sign up, see 1 signup in /admin/partners, then delete test data</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>46328</v>
+        <v>46319</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -2586,17 +2586,13 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>T09, T18</t>
-        </is>
-      </c>
+          <t>https://kolayxport.com/admin/partners</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Only after tracking is confirmed</t>
+          <t>With Claude d7; see Tests Q01</t>
         </is>
       </c>
       <c r="J24" s="4">
@@ -2607,12 +2603,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Fact-check the blog posts (2 a week)</t>
+          <t>Send the first partner messages (Varyant 5 / 6)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2621,7 +2617,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -2630,18 +2626,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>T09, T18</t>
+        </is>
+      </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Recurring every Tue/Thu</t>
+          <t>Only after tracking is confirmed</t>
         </is>
       </c>
       <c r="J25" s="4">
@@ -2652,12 +2652,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>First live demo in a partner group (scripted, 30 min)</t>
+          <t>Fact-check the blog posts (2 a week)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46344</v>
+        <v>46329</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -2678,9 +2678,17 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
+        </is>
+      </c>
       <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Recurring every Tue/Thu</t>
+        </is>
+      </c>
       <c r="J26" s="4">
         <f>IF(AND(D26&lt;&gt;"",D26&lt;TODAY(),E26&lt;&gt;"Done",E26&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2689,12 +2697,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Ask the first paying customers for written testimonial consent</t>
+          <t>First live demo in a partner group (scripted, 30 min)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2703,7 +2711,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>46365</v>
+        <v>46344</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -2712,14 +2720,10 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="4">
@@ -2730,21 +2734,21 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Phase 2: start Instagram organic (only if the gate passed)</t>
+          <t>Ask the first paying customers for written testimonial consent</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>46398</v>
+        <v>46365</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -2758,14 +2762,10 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="4">
         <f>IF(AND(D28&lt;&gt;"",D28&lt;TODAY(),E28&lt;&gt;"Done",E28&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -2775,43 +2775,43 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage A (capture, claim, admin report)</t>
+          <t>Phase 2: start Instagram organic (only if the gate passed)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>46314</v>
+        <v>46398</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Deployed b6ee9895</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="4">
         <f>IF(AND(D29&lt;&gt;"",D29&lt;TODAY(),E29&lt;&gt;"Done",E29&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2820,12 +2820,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>T25</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
+          <t>Referral Stage A (capture, claim, admin report)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2834,11 +2834,11 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>46333</v>
+        <v>46314</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2851,14 +2851,10 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Spec §3–6</t>
+          <t>Deployed b6ee9895</t>
         </is>
       </c>
       <c r="J30" s="4">
@@ -2869,12 +2865,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T26</t>
+          <t>T25</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
+          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2883,11 +2879,11 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>46314</v>
+        <v>46333</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2897,13 +2893,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Deployed d44c426e behind PRICING_V2 (flag off)</t>
+          <t>Spec §3–6</t>
         </is>
       </c>
       <c r="J31" s="4">
@@ -2914,12 +2914,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>T26b</t>
+          <t>T26</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P3: Stripe prices (all 14: yearly packages, Aylık, modules)</t>
+          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2937,18 +2937,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com/products</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Created live, inert behind PRICING_V2; code waiting for a deploy slot</t>
+          <t>Deployed d44c426e behind PRICING_V2 (flag off)</t>
         </is>
       </c>
       <c r="J32" s="4">
@@ -2959,17 +2959,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>T26b</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Decide taksit option</t>
+          <t>Pricing v2 P3: Stripe prices (all 14: yearly packages, Aylık, modules)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -2982,18 +2982,18 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+          <t>https://dashboard.stripe.com/products</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Decided: yearly = pay-in-full only (Stripe card); Aylık = no-commitment option; iyzico/PayTR dropped. Parked: real taksit only via a Turkish seller entity later</t>
+          <t>Created live, inert behind PRICING_V2; code waiting for a deploy slot</t>
         </is>
       </c>
       <c r="J33" s="4">
@@ -3004,30 +3004,30 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>T28</t>
+          <t>T27</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P4: /fiyatlandirma redesign (final amounts, no '+KDV')</t>
+          <t>Decide taksit option</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>46356</v>
+        <v>46314</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3035,12 +3035,12 @@
           <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>T05b, T27</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Decided: yearly = pay-in-full only (Stripe card); Aylık = no-commitment option; iyzico/PayTR dropped. Parked: real taksit only via a Turkish seller entity later</t>
+        </is>
+      </c>
       <c r="J34" s="4">
         <f>IF(AND(D34&lt;&gt;"",D34&lt;TODAY(),E34&lt;&gt;"Done",E34&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3049,12 +3049,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T29</t>
+          <t>T28</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Upload the remaining 8 tutorials</t>
+          <t>Pricing v2 P4: /fiyatlandirma redesign (final amounts, no '+KDV')</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3063,11 +3063,11 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>46315</v>
+        <v>46356</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3077,10 +3077,14 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>T05b, T27</t>
+        </is>
+      </c>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="4">
         <f>IF(AND(D35&lt;&gt;"",D35&lt;TODAY(),E35&lt;&gt;"Done",E35&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3090,12 +3094,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T29</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Blog cadence: 2 posts a week from the content calendar</t>
+          <t>Upload the remaining 8 tutorials</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -3104,11 +3108,11 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>46329</v>
+        <v>46315</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3118,14 +3122,10 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="4">
         <f>IF(AND(D36&lt;&gt;"",D36&lt;TODAY(),E36&lt;&gt;"Done",E36&lt;&gt;"Cancelled"),"OVERDUE","")</f>
@@ -3135,12 +3135,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T30</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
+          <t>Blog cadence: 2 posts a week from the content calendar</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>T07, T25</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr"/>
@@ -3180,12 +3180,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T31</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Privacy notice: one line on masked referrals shown to partners</t>
+          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3208,30 +3208,60 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Lawyer-review flag</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>T07, T25</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr"/>
       <c r="J38" s="4">
         <f>IF(AND(D38&lt;&gt;"",D38&lt;TODAY(),E38&lt;&gt;"Done",E38&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="8" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Privacy notice: one line on masked referrals shown to partners</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Lawyer-review flag</t>
+        </is>
+      </c>
       <c r="J39" s="4">
         <f>IF(AND(D39&lt;&gt;"",D39&lt;TODAY(),E39&lt;&gt;"Done",E39&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -29314,7 +29344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29888,20 +29918,24 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>YouTube Studio</t>
+          <t>Google Tag Manager (GTM-N6SW5T7K)</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
+          <t>https://tagmanager.google.com/?authuser=kolayxport@gmail.com#/container/accounts/6383523253/containers/267664935/workspaces/2</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
+          <t>Atilla, Merisa</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Account KolayXport (Tamsar, Inc.) on kolayxport@gmail.com; v2 published 19 Oct</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -29911,22 +29945,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Stripe dashboard (Tamsar, Inc.)</t>
+          <t>Google Analytics 4 (G-V4ZC6HS65N)</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com</t>
+          <t>https://analytics.google.com/analytics/web/?authuser=kolayxport@gmail.com#/a412601386p559673981/reports/intelligenthome</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Atilla, Merisa</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Coupons, promo codes, Global Payouts</t>
+          <t>Property kolayxport.com, Türkiye time zone; Merisa needs viewer access</t>
         </is>
       </c>
     </row>
@@ -29938,17 +29972,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Reklam Kurulu influencer guide (send to partners)</t>
+          <t>YouTube Studio</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>https://ticaret.gov.tr/haberler/ticaret-bakanligi-sosyal-medya-etkileyicileri-icin-kilavuz-yayimladi</t>
+          <t>https://studio.youtube.com</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Merisa, Ekin</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -29961,20 +29995,24 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Bionluk (freelancers)</t>
+          <t>Stripe dashboard (Tamsar, Inc.)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>https://bionluk.com</t>
+          <t>https://dashboard.stripe.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr"/>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Coupons, promo codes, Global Payouts</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -29984,38 +30022,70 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>Reklam Kurulu influencer guide (send to partners)</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>https://ticaret.gov.tr/haberler/ticaret-bakanligi-sosyal-medya-etkileyicileri-icin-kilavuz-yayimladi</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Merisa, Ekin</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Bionluk (freelancers)</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>https://bionluk.com</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>PraPazar packages (pricing reference)</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>https://prapazar.com/tr/paketler</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Atilla</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Checked 2026-10-19</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -30219,6 +30289,20 @@
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n"/>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n"/>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="8" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30248,6 +30332,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30259,7 +30345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30750,11 +30836,29 @@
       <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="A24" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Tracking accounts created under kolayxport@gmail.com: GTM container GTM-N6SW5T7K (account KolayXport (Tamsar, Inc.)) and GA4 property G-V4ZC6HS65N; GTM v2 published with GA4 base + funnel-event tags</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Atilla (asked Claude to do it)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>this session</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Google data-sharing options left off</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -31105,6 +31209,13 @@
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gtm/KolayXport-ERP.xlsx
+++ b/docs/gtm/KolayXport-ERP.xlsx
@@ -2608,20 +2608,20 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Send the first partner messages (Varyant 5 / 6)</t>
+          <t>Partner outreach materials ready (pack + wave-1 drafts)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Claude: orchestrator</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46328</v>
+        <v>46315</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2631,17 +2631,13 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>T09, T18</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/README.md</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Only after tracking is confirmed</t>
+          <t>Pushed 2a56d829 + 92046d3a; sending = T34/T36</t>
         </is>
       </c>
       <c r="J25" s="4">
@@ -2820,25 +2816,25 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T33</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage A (capture, claim, admin report)</t>
+          <t>Join the 5 wave-1 FB groups (M1–M5), write ≥3 helpful answers each, then fill [son konu] in drafts M1–M5</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>46314</v>
+        <v>46325</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2848,15 +2844,11 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/wave1_first_messages.md</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Deployed b6ee9895</t>
-        </is>
-      </c>
+      <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="4">
         <f>IF(AND(D30&lt;&gt;"",D30&lt;TODAY(),E30&lt;&gt;"Done",E30&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -2865,25 +2857,25 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T25</t>
+          <t>T34</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
+          <t>Send wave-1 first messages M1–M10 and set Status in the drafts file + Partner pipeline</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2893,17 +2885,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/wave1_first_messages.md</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T33, T18</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Spec §3–6</t>
+          <t>Only after the ?ref link test (T18)</t>
         </is>
       </c>
       <c r="J31" s="4">
@@ -2914,41 +2906,41 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>T26</t>
+          <t>T35</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
+          <t>Check whether 'Matesy' is Burak Çatak's own Etsy tool (E4); read Sedat Ateş's latest tweets (E5)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46314</v>
+        <v>46325</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/wave1_first_messages.md</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Deployed d44c426e behind PRICING_V2 (flag off)</t>
+          <t>If Matesy is his tool → wave 2, use Furkan Bircan or URS instead</t>
         </is>
       </c>
       <c r="J32" s="4">
@@ -2959,43 +2951,43 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T26b</t>
+          <t>T36</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P3: Stripe prices (all 14: yearly packages, Aylık, modules)</t>
+          <t>Send wave-1 first messages E1–E5 and set Status</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Claude: d7 (dev)</t>
+          <t>Ekin</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46314</v>
+        <v>46329</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com/products</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>Created live, inert behind PRICING_V2; code waiting for a deploy slot</t>
-        </is>
-      </c>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/wave1_first_messages.md</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>T35, T18</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="4">
         <f>IF(AND(D33&lt;&gt;"",D33&lt;TODAY(),E33&lt;&gt;"Done",E33&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3004,41 +2996,41 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>T27</t>
+          <t>T37</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Decide taksit option</t>
+          <t>Second research pass: Trendyol-seller and print-on-demand FB/Telegram groups</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Claude: to assign</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>46314</v>
+        <v>46332</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/shortlist-wave1.csv</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Decided: yearly = pay-in-full only (Stripe card); Aylık = no-commitment option; iyzico/PayTR dropped. Parked: real taksit only via a Turkish seller entity later</t>
+          <t>Gap found in wave-1 research</t>
         </is>
       </c>
       <c r="J34" s="4">
@@ -3049,43 +3041,39 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T28</t>
+          <t>T38</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Pricing v2 P4: /fiyatlandirma redesign (final amounts, no '+KDV')</t>
+          <t>Put this ERP into Google Sheets (kolayxport@gmail.com) and share with Merisa + Ekin</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Atilla</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>46356</v>
+        <v>46317</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>T05b, T27</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr"/>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Claude cannot use the native file picker; upload the .xlsx or let Claude try via Drive</t>
+        </is>
+      </c>
       <c r="J35" s="4">
         <f>IF(AND(D35&lt;&gt;"",D35&lt;TODAY(),E35&lt;&gt;"Done",E35&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3094,39 +3082,43 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>T29</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Upload the remaining 8 tutorials</t>
+          <t>Referral Stage A (capture, claim, admin report)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Deployed b6ee9895</t>
+        </is>
+      </c>
       <c r="J36" s="4">
         <f>IF(AND(D36&lt;&gt;"",D36&lt;TODAY(),E36&lt;&gt;"Done",E36&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3135,43 +3127,47 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T30</t>
+          <t>T25</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Blog cadence: 2 posts a week from the content calendar</t>
+          <t>Referral Stage B (bounty ledger, /app/ortaklik, Stripe Global Payouts)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>46329</v>
+        <v>46333</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr"/>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Spec §3–6</t>
+        </is>
+      </c>
       <c r="J37" s="4">
         <f>IF(AND(D37&lt;&gt;"",D37&lt;TODAY(),E37&lt;&gt;"Done",E37&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3180,43 +3176,43 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>T31</t>
+          <t>T26</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
+          <t>Pricing v2 P1: plan keys, yearly limits, modules</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>46333</v>
+        <v>46314</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>T07, T25</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr"/>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Deployed d44c426e behind PRICING_V2 (flag off)</t>
+        </is>
+      </c>
       <c r="J38" s="4">
         <f>IF(AND(D38&lt;&gt;"",D38&lt;TODAY(),E38&lt;&gt;"Done",E38&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -3225,25 +3221,25 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T32</t>
+          <t>T26b</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Privacy notice: one line on masked referrals shown to partners</t>
+          <t>Pricing v2 P3: Stripe prices (all 14: yearly packages, Aylık, modules)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Claude: gtm-overhaul</t>
+          <t>Claude: d7 (dev)</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>46333</v>
+        <v>46314</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3253,13 +3249,13 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+          <t>https://dashboard.stripe.com/products</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Lawyer-review flag</t>
+          <t>Created live, inert behind PRICING_V2; code waiting for a deploy slot</t>
         </is>
       </c>
       <c r="J39" s="4">
@@ -3268,90 +3264,266 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="8" t="n"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Decide taksit option</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Decided: yearly = pay-in-full only (Stripe card); Aylık = no-commitment option; iyzico/PayTR dropped. Parked: real taksit only via a Turkish seller entity later</t>
+        </is>
+      </c>
       <c r="J40" s="4">
         <f>IF(AND(D40&lt;&gt;"",D40&lt;TODAY(),E40&lt;&gt;"Done",E40&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="8" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>T28</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Pricing v2 P4: /fiyatlandirma redesign (final amounts, no '+KDV')</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/pricing-v2.md</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>T05b, T27</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="4">
         <f>IF(AND(D41&lt;&gt;"",D41&lt;TODAY(),E41&lt;&gt;"Done",E41&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="8" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>T29</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Upload the remaining 8 tutorials</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="4">
         <f>IF(AND(D42&lt;&gt;"",D42&lt;TODAY(),E42&lt;&gt;"Done",E42&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="8" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Blog cadence: 2 posts a week from the content calendar</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>46329</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="4">
         <f>IF(AND(D43&lt;&gt;"",D43&lt;TODAY(),E43&lt;&gt;"Done",E43&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="8" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Draft the /ortaklik partner-terms page (publish after Stage B + accountant)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/turkey-gameplan.md</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>T07, T25</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="4">
         <f>IF(AND(D44&lt;&gt;"",D44&lt;TODAY(),E44&lt;&gt;"Done",E44&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="8" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Privacy notice: one line on masked referrals shown to partners</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Claude: gtm-overhaul</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/referral-spec.md</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Lawyer-review flag</t>
+        </is>
+      </c>
       <c r="J45" s="4">
         <f>IF(AND(D45&lt;&gt;"",D45&lt;TODAY(),E45&lt;&gt;"Done",E45&lt;&gt;"Cancelled"),"OVERDUE","")</f>
         <v/>
@@ -7576,15 +7748,47 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>P023</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye Yardımlaşma Platformu</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/etsytr/</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>48018</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5">
         <f>IF(J27="","",J27+4)</f>
@@ -7613,18 +7817,54 @@
       <c r="W27" s="13" t="n"/>
       <c r="X27" s="14" t="n"/>
       <c r="Y27" s="14" t="n"/>
-      <c r="Z27" s="8" t="n"/>
+      <c r="Z27" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M1 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Largest active TR Etsy help group (private, Denizli, since 2020). Rules ban promo/spam: pitch admins for an official partner post, not member posts. Probably the same org as t.me/etsyturkiyeyardimlasmagrubu.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>AMAZON FBA SELLER GRUBU</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/amazondestek/</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5">
         <f>IF(J28="","",J28+4)</f>
@@ -7653,18 +7893,54 @@
       <c r="W28" s="13" t="n"/>
       <c r="X28" s="14" t="n"/>
       <c r="Y28" s="14" t="n"/>
-      <c r="Z28" s="8" t="n"/>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M2 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: URL now redirects to /groups/exportpartnersturkiye, renamed 'E-Commerce Sellers and Suppliers Türkiye Network' (2026-10-20). | TR sellers on Amazon/Etsy/Shopify/Walmart plus suppliers (#ihracat). Rules allow manufacturers to share a website link without visuals, so some announcements are tolerated.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ETSY TÜRKİYE -Mikro ihracat</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1392403800958676/</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="5">
         <f>IF(J29="","",J29+4)</f>
@@ -7693,18 +7969,54 @@
       <c r="W29" s="13" t="n"/>
       <c r="X29" s="14" t="n"/>
       <c r="Y29" s="14" t="n"/>
-      <c r="Z29" s="8" t="n"/>
+      <c r="Z29" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M3 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Public Etsy/micro-export group. Loosely moderated (an off-topic wholesale post was visible).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>P026</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>E-Ticaret Yardımlaşma (Trendyol &amp; HepsiBurada &amp; Etsy &amp; Amazon &amp; Dropship)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/eticaretpazaryeri/</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5">
         <f>IF(J30="","",J30+4)</f>
@@ -7733,18 +8045,54 @@
       <c r="W30" s="13" t="n"/>
       <c r="X30" s="14" t="n"/>
       <c r="Y30" s="14" t="n"/>
-      <c r="Z30" s="8" t="n"/>
+      <c r="Z30" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M4 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Very active mixed group: Trendyol/HB plus Etsy/Amazon. Fits the Trendyol-to-abroad angle.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>E-Ticaret Türkiye (group)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/eticareturkiye/</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="5">
         <f>IF(J31="","",J31+4)</f>
@@ -7773,18 +8121,54 @@
       <c r="W31" s="13" t="n"/>
       <c r="X31" s="14" t="n"/>
       <c r="Y31" s="14" t="n"/>
-      <c r="Z31" s="8" t="n"/>
+      <c r="Z31" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Public e-commerce/export group run by the same E-Ticaret Türkiye brand as YouTube @eticareturkiye (46K, holds city events). Org admin is reachable.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Akın Yılmaz ile Yapay Zeka Destekli Dropshipping E-Ticaret Amazon eBay Shop</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ebayamazonshopifyturkiyedropshipping/</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>30600</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5">
         <f>IF(J32="","",J32+4)</f>
@@ -7813,18 +8197,54 @@
       <c r="W32" s="13" t="n"/>
       <c r="X32" s="14" t="n"/>
       <c r="Y32" s="14" t="n"/>
-      <c r="Z32" s="8" t="n"/>
+      <c r="Z32" s="8" t="inlineStr">
+        <is>
+          <t>DO NOT CONTACT (income-promise marketing). Shortlist 2026-10-20: Public TR group for Amazon/eBay/Shopify dropshipping, led by Akın Yılmaz (Okyanusi). COURSE SELLER with income-style marketing on his YouTube.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>P029</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye Yardımlaşma</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/230855325101291/</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>9300</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="5">
         <f>IF(J33="","",J33+4)</f>
@@ -7853,18 +8273,54 @@
       <c r="W33" s="13" t="n"/>
       <c r="X33" s="14" t="n"/>
       <c r="Y33" s="14" t="n"/>
-      <c r="Z33" s="8" t="n"/>
+      <c r="Z33" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M5 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Public TR Etsy sellers knowledge-sharing group. Activity looks moderate.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>P030</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>ETSY Türkiye Satıcılar Yardımlaşma</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1403308160115275/</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5">
         <f>IF(J34="","",J34+4)</f>
@@ -7893,18 +8349,54 @@
       <c r="W34" s="13" t="n"/>
       <c r="X34" s="14" t="n"/>
       <c r="Y34" s="14" t="n"/>
-      <c r="Z34" s="8" t="n"/>
+      <c r="Z34" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Public group. Members share products for traffic, so promo posts seem tolerated.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>P031</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye - Mikro İhracat</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/etsyturkiye/</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>29155</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5">
         <f>IF(J35="","",J35+4)</f>
@@ -7933,18 +8425,54 @@
       <c r="W35" s="13" t="n"/>
       <c r="X35" s="14" t="n"/>
       <c r="Y35" s="14" t="n"/>
-      <c r="Z35" s="8" t="n"/>
+      <c r="Z35" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Large old (2016) private Etsy/micro-export group with low current activity. Rules allow affiliate links if disclosed.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>P032</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye Yardımlaşma ve Destek</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/etsyturkiyeyardimlasma/</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>2647</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5">
         <f>IF(J36="","",J36+4)</f>
@@ -7973,18 +8501,54 @@
       <c r="W36" s="13" t="n"/>
       <c r="X36" s="14" t="n"/>
       <c r="Y36" s="14" t="n"/>
-      <c r="Z36" s="8" t="n"/>
+      <c r="Z36" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Public group created 2025, managed by Etsi Medya (Etsy Danışmanlık), a consultancy: admin is reachable but may compete.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>P033</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>ETSY BİLGİ PAYLAŞIM GURUBU</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/713974435622635/</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5">
         <f>IF(J37="","",J37+4)</f>
@@ -8013,18 +8577,54 @@
       <c r="W37" s="13" t="n"/>
       <c r="X37" s="14" t="n"/>
       <c r="Y37" s="14" t="n"/>
-      <c r="Z37" s="8" t="n"/>
+      <c r="Z37" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Private Etsy idea-sharing group (2018). Low activity.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>P034</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>2025 E-Ticaret Rehberi (Trendyol, Hepsiburada, N11, Amazon, Etsy)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/698339230982728/</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5">
         <f>IF(J38="","",J38+4)</f>
@@ -8053,18 +8653,54 @@
       <c r="W38" s="13" t="n"/>
       <c r="X38" s="14" t="n"/>
       <c r="Y38" s="14" t="n"/>
-      <c r="Z38" s="8" t="n"/>
+      <c r="Z38" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Private mixed marketplace group (domestic plus Amazon/Etsy).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>P035</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>E-Ticaret Satıcıları-N11-Gittigidiyor-Hepsiburada-Trendyol-Amazon.com.tr</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/406000266951806/</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>48600</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5">
         <f>IF(J39="","",J39+4)</f>
@@ -8093,18 +8729,54 @@
       <c r="W39" s="13" t="n"/>
       <c r="X39" s="14" t="n"/>
       <c r="Y39" s="14" t="n"/>
-      <c r="Z39" s="8" t="n"/>
+      <c r="Z39" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Big domestic-marketplace seller group. Bans product/service promo and video posts. Mostly a domestic fit.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>P036</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Türkiye Amazon</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/TurkiyeAmazon/</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>30900</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="5">
         <f>IF(J40="","",J40+4)</f>
@@ -8133,18 +8805,54 @@
       <c r="W40" s="13" t="n"/>
       <c r="X40" s="14" t="n"/>
       <c r="Y40" s="14" t="n"/>
-      <c r="Z40" s="8" t="n"/>
+      <c r="Z40" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Large but nearly dormant Amazon group (2017). Bans promo.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>P037</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>ETSY EĞİTİM PLATFORMU</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/398367145218775/</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="5">
         <f>IF(J41="","",J41+4)</f>
@@ -8173,18 +8881,52 @@
       <c r="W41" s="13" t="n"/>
       <c r="X41" s="14" t="n"/>
       <c r="Y41" s="14" t="n"/>
-      <c r="Z41" s="8" t="n"/>
+      <c r="Z41" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Public Etsy education group, dormant.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>P038</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>E-ticaret N11 Trendyol Hepsiburada Gittigidiyor Amazon (group)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/2428739190743849/</t>
+        </is>
+      </c>
       <c r="F42" s="12" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
+      <c r="G42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="5">
         <f>IF(J42="","",J42+4)</f>
@@ -8213,18 +8955,52 @@
       <c r="W42" s="13" t="n"/>
       <c r="X42" s="14" t="n"/>
       <c r="Y42" s="14" t="n"/>
-      <c r="Z42" s="8" t="n"/>
+      <c r="Z42" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Domestic marketplace seller group. Page needs login; counts not visible. Appears in search results today.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Ebay Dropshipping Turkiye (FB group)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/ebaydropshippingturkiye/</t>
+        </is>
+      </c>
       <c r="F43" s="12" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
+      <c r="G43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="5">
         <f>IF(J43="","",J43+4)</f>
@@ -8253,18 +9029,52 @@
       <c r="W43" s="13" t="n"/>
       <c r="X43" s="14" t="n"/>
       <c r="Y43" s="14" t="n"/>
-      <c r="Z43" s="8" t="n"/>
+      <c r="Z43" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: TR eBay dropshipping group. Page needs login; counts not visible. Appears in search results today.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye (group 268451884056697)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/268451884056697/</t>
+        </is>
+      </c>
       <c r="F44" s="12" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
+      <c r="G44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="5">
         <f>IF(J44="","",J44+4)</f>
@@ -8293,18 +9103,54 @@
       <c r="W44" s="13" t="n"/>
       <c r="X44" s="14" t="n"/>
       <c r="Y44" s="14" t="n"/>
-      <c r="Z44" s="8" t="n"/>
+      <c r="Z44" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy Türkiye group seen in search results. Page content not readable without login.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>ETSY Türkiye POD Grubu Tote Bag Tshirt Sweatshirt</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/printondemandturkiye/</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>325</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="5">
         <f>IF(J45="","",J45+4)</f>
@@ -8333,18 +9179,54 @@
       <c r="W45" s="13" t="n"/>
       <c r="X45" s="14" t="n"/>
       <c r="Y45" s="14" t="n"/>
-      <c r="Z45" s="8" t="n"/>
+      <c r="Z45" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Small private Etsy POD group (2018). Rare POD-specific fit.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>E-İhracat Yardımlaşma Platformu</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/eihracat</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="5">
         <f>IF(J46="","",J46+4)</f>
@@ -8373,18 +9255,54 @@
       <c r="W46" s="13" t="n"/>
       <c r="X46" s="14" t="n"/>
       <c r="Y46" s="14" t="n"/>
-      <c r="Z46" s="8" t="n"/>
+      <c r="Z46" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Exact topic fit (e-ihracat) but dormant private group. An admin could be asked to revive it.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>E-Ticaret, E-İhracat &amp; Pazaryerleri Bilgi ve Yardımlaşma Platformu</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/eticaretgrubu/</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>632</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="5">
         <f>IF(J47="","",J47+4)</f>
@@ -8413,18 +9331,54 @@
       <c r="W47" s="13" t="n"/>
       <c r="X47" s="14" t="n"/>
       <c r="Y47" s="14" t="n"/>
-      <c r="Z47" s="8" t="n"/>
+      <c r="Z47" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Small dormant e-commerce/export group.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>P044</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye (group 1480525006149352)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/1480525006149352/</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="5">
         <f>IF(J48="","",J48+4)</f>
@@ -8453,18 +9407,52 @@
       <c r="W48" s="13" t="n"/>
       <c r="X48" s="14" t="n"/>
       <c r="Y48" s="14" t="n"/>
-      <c r="Z48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Tiny public Etsy TR group (2024).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Amazon FBA - Turkey (page)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amazonturkey/</t>
+        </is>
+      </c>
       <c r="F49" s="12" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
+      <c r="G49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="5">
         <f>IF(J49="","",J49+4)</f>
@@ -8493,18 +9481,52 @@
       <c r="W49" s="13" t="n"/>
       <c r="X49" s="14" t="n"/>
       <c r="Y49" s="14" t="n"/>
-      <c r="Z49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Community page that says it aims to bring Turkish Amazon sellers together. Counts not visible logged-out.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n"/>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>E-İhracat Türkiye (page)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eihracatturkiye/</t>
+        </is>
+      </c>
       <c r="F50" s="12" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
+      <c r="G50" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="5">
         <f>IF(J50="","",J50+4)</f>
@@ -8533,18 +9555,52 @@
       <c r="W50" s="13" t="n"/>
       <c r="X50" s="14" t="n"/>
       <c r="Y50" s="14" t="n"/>
-      <c r="Z50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-export platform page (Istanbul). Same brand as X @eihracatturkiye (201 followers). Counts not visible.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>EtsyAcademy (page)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/etsyakademi/</t>
+        </is>
+      </c>
       <c r="F51" s="12" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
+      <c r="G51" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="5">
         <f>IF(J51="","",J51+4)</f>
@@ -8573,18 +9629,54 @@
       <c r="W51" s="13" t="n"/>
       <c r="X51" s="14" t="n"/>
       <c r="Y51" s="14" t="n"/>
-      <c r="Z51" s="8" t="n"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Page by a multi-shop Etsy/POD seller that advertises paid online Etsy trainings. COURSE SELLER.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Turkiye Ebay, Amazon, Shopify Dropshipping UK &amp; USA Eğitmenlik Merkezi (page)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>fb_admin</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ebayturkiyedropshipping/</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>992</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="5">
         <f>IF(J52="","",J52+4)</f>
@@ -8613,18 +9705,54 @@
       <c r="W52" s="13" t="n"/>
       <c r="X52" s="14" t="n"/>
       <c r="Y52" s="14" t="n"/>
-      <c r="Z52" s="8" t="n"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Dropshipping training page. COURSE SELLER.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Etsy Türkiye Yardımlaşma Grubu (@etsyturkiyeyardimlasmagrubu)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/etsyturkiyeyardimlasmagrubu</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>7949</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="5">
         <f>IF(J53="","",J53+4)</f>
@@ -8653,18 +9781,54 @@
       <c r="W53" s="13" t="n"/>
       <c r="X53" s="14" t="n"/>
       <c r="Y53" s="14" t="n"/>
-      <c r="Z53" s="8" t="n"/>
+      <c r="Z53" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy TR help group. Its description matches the FB etsytr platform (likely same admins), so coordinate with that row.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>AMAZON DROPSHIPPING TURKİYE (MZN Danışmanlık)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/dropshippingmzn</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>5545</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="5">
         <f>IF(J54="","",J54+4)</f>
@@ -8693,18 +9857,54 @@
       <c r="W54" s="13" t="n"/>
       <c r="X54" s="14" t="n"/>
       <c r="Y54" s="14" t="n"/>
-      <c r="Z54" s="8" t="n"/>
+      <c r="Z54" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Run by MZN Danışmanlık (Amazon training/consulting firm, YouTube 18.9K). Reachable company admin. Course/consulting seller.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>E-ticaret &amp; Dropshopping &amp; Stoksuz satış (@eticaretlab)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/eticaretlab</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>3739</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="5">
         <f>IF(J55="","",J55+4)</f>
@@ -8733,18 +9933,54 @@
       <c r="W55" s="13" t="n"/>
       <c r="X55" s="14" t="n"/>
       <c r="Y55" s="14" t="n"/>
-      <c r="Z55" s="8" t="n"/>
+      <c r="Z55" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Mostly domestic Trendyol/HB plus dropshipping and suppliers.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>eBay Dropshipping Türkiye - Justrun Akademi</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/ebaydropshippingg</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5">
         <f>IF(J56="","",J56+4)</f>
@@ -8773,18 +10009,54 @@
       <c r="W56" s="13" t="n"/>
       <c r="X56" s="14" t="n"/>
       <c r="Y56" s="14" t="n"/>
-      <c r="Z56" s="8" t="n"/>
+      <c r="Z56" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: eBay dropshipping community run by Justrun Akademi (training brand).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Amazon Global Seller Group 🇹🇷</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/AmazonGlobalSellergroup</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>1614</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="5">
         <f>IF(J57="","",J57+4)</f>
@@ -8813,18 +10085,54 @@
       <c r="W57" s="13" t="n"/>
       <c r="X57" s="14" t="n"/>
       <c r="Y57" s="14" t="n"/>
-      <c r="Z57" s="8" t="n"/>
+      <c r="Z57" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Free Q&amp;A group for TR global Amazon sellers. Ads prohibited: admin approval is needed.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Ticaret Var Burada (Foreigntrade.tc Club)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/ticaretvarburada</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>1272</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5">
         <f>IF(J58="","",J58+4)</f>
@@ -8853,18 +10161,54 @@
       <c r="W58" s="13" t="n"/>
       <c r="X58" s="14" t="n"/>
       <c r="Y58" s="14" t="n"/>
-      <c r="Z58" s="8" t="n"/>
+      <c r="Z58" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: General trade/import-export club group, run by a club org.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Gürkan zone (Telegram)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/gurkanzonetg</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>733</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5">
         <f>IF(J59="","",J59+4)</f>
@@ -8893,18 +10237,54 @@
       <c r="W59" s="13" t="n"/>
       <c r="X59" s="14" t="n"/>
       <c r="Y59" s="14" t="n"/>
-      <c r="Z59" s="8" t="n"/>
+      <c r="Z59" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-commerce/Shopify dropshipping community of Gürkan Ordueri (YouTube 311K, X 38.8K). DMs to members are banned.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Özgün'Ecom | Amazon | Shopify | eBay</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/amazonbilgini</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="5">
         <f>IF(J60="","",J60+4)</f>
@@ -8933,18 +10313,54 @@
       <c r="W60" s="13" t="n"/>
       <c r="X60" s="14" t="n"/>
       <c r="Y60" s="14" t="n"/>
-      <c r="Z60" s="8" t="n"/>
+      <c r="Z60" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Global e-commerce support channel (owner linktree ozguninceli).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Amazon Türkiye (FBM-FBA-PL)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/+EJOdsdxEPSg1OWY0</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>345</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="5">
         <f>IF(J61="","",J61+4)</f>
@@ -8973,18 +10389,54 @@
       <c r="W61" s="13" t="n"/>
       <c r="X61" s="14" t="n"/>
       <c r="Y61" s="14" t="n"/>
-      <c r="Z61" s="8" t="n"/>
+      <c r="Z61" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Small Amazon FBM/FBA/PL group (public invite page).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Trendyol Satıcı Destek Grubu</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/trendyolsatkazan</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="5">
         <f>IF(J62="","",J62+4)</f>
@@ -9013,18 +10465,54 @@
       <c r="W62" s="13" t="n"/>
       <c r="X62" s="14" t="n"/>
       <c r="Y62" s="14" t="n"/>
-      <c r="Z62" s="8" t="n"/>
+      <c r="Z62" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Small Trendyol seller support group. Domestic fit.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Amazon Online Arbitrage E-ticaret</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/onlinearbitraj</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="5">
         <f>IF(J63="","",J63+4)</f>
@@ -9053,18 +10541,54 @@
       <c r="W63" s="13" t="n"/>
       <c r="X63" s="14" t="n"/>
       <c r="Y63" s="14" t="n"/>
-      <c r="Z63" s="8" t="n"/>
+      <c r="Z63" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Small Amazon OA discussion group.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>bayaffluence Amazon fba-fbm-dropshipping destek topluluğu</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/s/bayaffluence</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="5">
         <f>IF(J64="","",J64+4)</f>
@@ -9093,18 +10617,52 @@
       <c r="W64" s="13" t="n"/>
       <c r="X64" s="14" t="n"/>
       <c r="Y64" s="14" t="n"/>
-      <c r="Z64" s="8" t="n"/>
+      <c r="Z64" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Tiny Amazon channel. Probably inactive.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>e-ticaret @ TECRÜBE PAYLAŞIM</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>tg_admin</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Telegram</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>https://t.me/+rxRlrq6Bly42Yzkx</t>
+        </is>
+      </c>
       <c r="F65" s="12" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
+      <c r="G65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="5">
         <f>IF(J65="","",J65+4)</f>
@@ -9133,18 +10691,54 @@
       <c r="W65" s="13" t="n"/>
       <c r="X65" s="14" t="n"/>
       <c r="Y65" s="14" t="n"/>
-      <c r="Z65" s="8" t="n"/>
+      <c r="Z65" s="8" t="inlineStr">
+        <is>
+          <t>UNVERIFIED link. Shortlist 2026-10-20: E-commerce experience-sharing group (from search snippet). Invite page shows no title or count.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>P062</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Ahmet Konak (@koneeek)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/koneeek</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>36313</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="n"/>
       <c r="K66" s="5">
         <f>IF(J66="","",J66+4)</f>
@@ -9173,18 +10767,54 @@
       <c r="W66" s="13" t="n"/>
       <c r="X66" s="14" t="n"/>
       <c r="Y66" s="14" t="n"/>
-      <c r="Z66" s="8" t="n"/>
+      <c r="Z66" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 2 (tool founder, contact after 2–3 wave-1 partners are signed). Shortlist 2026-10-20: WAVE 2 (orchestrator 2026-10-20): contact only after 2–3 wave-1 partners are signed. Pitch the complementary angle: Optimsy = Etsy listings; KolayXport = multi-marketplace orders, finance/net profit, stock → referral or integration. Don't lead with listing-SEO. If he reads as a competitor, drop it p</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Selim Özdemir (@S_Ozdemir_)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/S_Ozdemir_</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>64261</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="5">
         <f>IF(J67="","",J67+4)</f>
@@ -9213,18 +10843,54 @@
       <c r="W67" s="13" t="n"/>
       <c r="X67" s="14" t="n"/>
       <c r="Y67" s="14" t="n"/>
-      <c r="Z67" s="8" t="n"/>
+      <c r="Z67" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft E1 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Amazon/Etsy seller voice with free education videos. Warns against paid courses (good trust signal).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>P064</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Furkan Bircan (@FurkanBircan)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/FurkanBircan</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>18727</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="5">
         <f>IF(J68="","",J68+4)</f>
@@ -9253,18 +10919,54 @@
       <c r="W68" s="13" t="n"/>
       <c r="X68" s="14" t="n"/>
       <c r="Y68" s="14" t="n"/>
-      <c r="Z68" s="8" t="n"/>
+      <c r="Z68" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Amazon FBA seller/educator.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Gürkan Ordueri (@Gurkanzone)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/Gurkanzone</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>38849</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J69" s="5" t="n"/>
       <c r="K69" s="5">
         <f>IF(J69="","",J69+4)</f>
@@ -9293,18 +10995,54 @@
       <c r="W69" s="13" t="n"/>
       <c r="X69" s="14" t="n"/>
       <c r="Y69" s="14" t="n"/>
-      <c r="Z69" s="8" t="n"/>
+      <c r="Z69" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Shopify/global e-commerce founder (Fellow Lemon, Revendify). YouTube 311K. Sells training.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Abdullah Yılmaz (@ASAPabdllh)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/ASAPabdllh</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>7796</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="n"/>
       <c r="K70" s="5">
         <f>IF(J70="","",J70+4)</f>
@@ -9333,18 +11071,54 @@
       <c r="W70" s="13" t="n"/>
       <c r="X70" s="14" t="n"/>
       <c r="Y70" s="14" t="n"/>
-      <c r="Z70" s="8" t="n"/>
+      <c r="Z70" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy product research/listing content. COURSE SELLER (1:1 coaching + "özel kamp").</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="12" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>P067</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Betül Korkmaz (@abetullk)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/abetullk</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>9565</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="5">
         <f>IF(J71="","",J71+4)</f>
@@ -9373,18 +11147,54 @@
       <c r="W71" s="13" t="n"/>
       <c r="X71" s="14" t="n"/>
       <c r="Y71" s="14" t="n"/>
-      <c r="Z71" s="8" t="n"/>
+      <c r="Z71" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy sales-troubleshooting threads ("Üretir ve Satamaz").</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>P068</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Mesut Berkant Yiğit (@mberkantyigit)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/mberkantyigit</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>5844</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="5">
         <f>IF(J72="","",J72+4)</f>
@@ -9413,18 +11223,54 @@
       <c r="W72" s="13" t="n"/>
       <c r="X72" s="14" t="n"/>
       <c r="Y72" s="14" t="n"/>
-      <c r="Z72" s="8" t="n"/>
+      <c r="Z72" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy digital products. Runs an Etsy digital-product training (COURSE SELLER).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>P069</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Erman Doğan (@ermandgn)</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/ermandgn</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>5547</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="5">
         <f>IF(J73="","",J73+4)</f>
@@ -9453,18 +11299,54 @@
       <c r="W73" s="13" t="n"/>
       <c r="X73" s="14" t="n"/>
       <c r="Y73" s="14" t="n"/>
-      <c r="Z73" s="8" t="n"/>
+      <c r="Z73" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Etsy seller trainings and design ideas. Runs a free community (EtsyPro).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>P070</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Eren Anderoğlu (@ErenAnderoglu)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/ErenAnderoglu</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>5363</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="5">
         <f>IF(J74="","",J74+4)</f>
@@ -9493,18 +11375,54 @@
       <c r="W74" s="13" t="n"/>
       <c r="X74" s="14" t="n"/>
       <c r="Y74" s="14" t="n"/>
-      <c r="Z74" s="8" t="n"/>
+      <c r="Z74" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Manufacturer and e-export voice on Amazon Handmade. Did live sessions with PrinWork.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>P071</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Serhat Sönmez (@serhatsonmez_)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/serhatsonmez_</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>5204</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="5">
         <f>IF(J75="","",J75+4)</f>
@@ -9533,18 +11451,54 @@
       <c r="W75" s="13" t="n"/>
       <c r="X75" s="14" t="n"/>
       <c r="Y75" s="14" t="n"/>
-      <c r="Z75" s="8" t="n"/>
+      <c r="Z75" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Exporter/Amazon seller, Amazon Handmade guides. Paid mentorship (statixpartner): COURSE SELLER.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Sedat Ateş (@sedat_ates)</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/sedat_ates</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>10606</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="5">
         <f>IF(J76="","",J76+4)</f>
@@ -9573,18 +11527,54 @@
       <c r="W76" s="13" t="n"/>
       <c r="X76" s="14" t="n"/>
       <c r="Y76" s="14" t="n"/>
-      <c r="Z76" s="8" t="n"/>
+      <c r="Z76" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft E5 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: E-commerce and e-export strategist, TEDx speaker. Posts e-ihracat incentive updates.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>P073</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Ertuğrul Yılmaz (@1ertugrulyilmaz)</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/1ertugrulyilmaz</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>4538</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="5">
         <f>IF(J77="","",J77+4)</f>
@@ -9613,18 +11603,54 @@
       <c r="W77" s="13" t="n"/>
       <c r="X77" s="14" t="n"/>
       <c r="Y77" s="14" t="n"/>
-      <c r="Z77" s="8" t="n"/>
+      <c r="Z77" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: "Digital artisan" selling globally from the Black Sea region. Posts on Amazon and Etsy digital products.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n"/>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="12" t="n"/>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>P074</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>TurkishExporter (@TurkshExporter)</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/TurkshExporter</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>39510</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="5">
         <f>IF(J78="","",J78+4)</f>
@@ -9653,18 +11679,54 @@
       <c r="W78" s="13" t="n"/>
       <c r="X78" s="14" t="n"/>
       <c r="Y78" s="14" t="n"/>
-      <c r="Z78" s="8" t="n"/>
+      <c r="Z78" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: B2B e-export platform plus export newsletter (ihracat.com.tr). Large reach, but B2B-leaning.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="8" t="n"/>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>P075</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Yasin Ölmez (@yasinolmez)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/yasinolmez</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>16653</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="5">
         <f>IF(J79="","",J79+4)</f>
@@ -9693,18 +11755,54 @@
       <c r="W79" s="13" t="n"/>
       <c r="X79" s="14" t="n"/>
       <c r="Y79" s="14" t="n"/>
-      <c r="Z79" s="8" t="n"/>
+      <c r="Z79" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Entrepreneur/e-commerce/marketing voice. Posts realistic takes on Etsy and Amazon.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n"/>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>P076</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Mustafa Namoğlu (@mustafa_namoglu)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/mustafa_namoglu</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>22383</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="5">
         <f>IF(J80="","",J80+4)</f>
@@ -9733,18 +11831,54 @@
       <c r="W80" s="13" t="n"/>
       <c r="X80" s="14" t="n"/>
       <c r="Y80" s="14" t="n"/>
-      <c r="Z80" s="8" t="n"/>
+      <c r="Z80" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: ikas executive. Talks to many small TR e-commerce SMBs. Domestic-store focus, possibly a channel partner.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>P077</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Bekir İlhan (@becqir)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/becqir</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>11944</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="n"/>
       <c r="K81" s="5">
         <f>IF(J81="","",J81+4)</f>
@@ -9773,18 +11907,54 @@
       <c r="W81" s="13" t="n"/>
       <c r="X81" s="14" t="n"/>
       <c r="Y81" s="14" t="n"/>
-      <c r="Z81" s="8" t="n"/>
+      <c r="Z81" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Omnichannel e-commerce entrepreneur. Wrote a widely shared Etsy account-closure thread.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n"/>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="4" t="n"/>
-      <c r="D82" s="4" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="4" t="n"/>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>P078</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Fatih Adak (@fatihadkdijital)</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/fatihadkdijital</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>5469</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="n"/>
       <c r="K82" s="5">
         <f>IF(J82="","",J82+4)</f>
@@ -9813,18 +11983,54 @@
       <c r="W82" s="13" t="n"/>
       <c r="X82" s="14" t="n"/>
       <c r="Y82" s="14" t="n"/>
-      <c r="Z82" s="8" t="n"/>
+      <c r="Z82" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-commerce brand/Klaviyo email marketing writer. Generic fit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n"/>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>P079</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Mert Tanciğer (@MertTanciger)</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/MertTanciger</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>1571</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="5">
         <f>IF(J83="","",J83+4)</f>
@@ -9853,18 +12059,54 @@
       <c r="W83" s="13" t="n"/>
       <c r="X83" s="14" t="n"/>
       <c r="Y83" s="14" t="n"/>
-      <c r="Z83" s="8" t="n"/>
+      <c r="Z83" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Exporter/researcher with a 254K YouTube (e-ticaret/e-ihracat). Better reached via YouTube.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n"/>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Yahyahan Kaya (@yahyahankaya)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/yahyahankaya</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>3789</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="5">
         <f>IF(J84="","",J84+4)</f>
@@ -9893,18 +12135,54 @@
       <c r="W84" s="13" t="n"/>
       <c r="X84" s="14" t="n"/>
       <c r="Y84" s="14" t="n"/>
-      <c r="Z84" s="8" t="n"/>
+      <c r="Z84" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-commerce voice who posts Etsy ads/feature updates. Low tweet volume (182).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="4" t="n"/>
-      <c r="D85" s="4" t="n"/>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="4" t="n"/>
-      <c r="H85" s="4" t="n"/>
-      <c r="I85" s="4" t="n"/>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>P081</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Can Özer (@thecanozer)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/thecanozer</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>4176</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="5">
         <f>IF(J85="","",J85+4)</f>
@@ -9933,18 +12211,54 @@
       <c r="W85" s="13" t="n"/>
       <c r="X85" s="14" t="n"/>
       <c r="Y85" s="14" t="n"/>
-      <c r="Z85" s="8" t="n"/>
+      <c r="Z85" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Offshore/US company formation (Sirket.io). Etsy/Amazon Handmade/Faire tips for TR sellers.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n"/>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Melih Çat (@melih_cat)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/melih_cat</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>41246</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="5">
         <f>IF(J86="","",J86+4)</f>
@@ -9973,18 +12287,54 @@
       <c r="W86" s="13" t="n"/>
       <c r="X86" s="14" t="n"/>
       <c r="Y86" s="14" t="n"/>
-      <c r="Z86" s="8" t="n"/>
+      <c r="Z86" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Growth-hacking/ads voice who comments on ikas vs Shopify. Generic e-commerce fit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>PrinWork (@prinworkcom)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/prinworkcom</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>777</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="5">
         <f>IF(J87="","",J87+4)</f>
@@ -10013,18 +12363,54 @@
       <c r="W87" s="13" t="n"/>
       <c r="X87" s="14" t="n"/>
       <c r="Y87" s="14" t="n"/>
-      <c r="Z87" s="8" t="n"/>
+      <c r="Z87" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-export maker-seller marketplace plus PrinWork Akademi. Runs live sessions (Amazon Handmade). Possible co-marketing.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n"/>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>farukecommerce (@farukcommerce)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/farukcommerce</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>281</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="5">
         <f>IF(J88="","",J88+4)</f>
@@ -10053,18 +12439,54 @@
       <c r="W88" s="13" t="n"/>
       <c r="X88" s="14" t="n"/>
       <c r="Y88" s="14" t="n"/>
-      <c r="Z88" s="8" t="n"/>
+      <c r="Z88" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Global e-commerce director, Etsy and Amazon seller. Small reach.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="12" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>P085</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>E-İhracat Türkiye (@eihracatTR)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/eihracattr</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="5">
         <f>IF(J89="","",J89+4)</f>
@@ -10093,18 +12515,54 @@
       <c r="W89" s="13" t="n"/>
       <c r="X89" s="14" t="n"/>
       <c r="Y89" s="14" t="n"/>
-      <c r="Z89" s="8" t="n"/>
+      <c r="Z89" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-ihracat info account, only 11 tweets.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n"/>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="12" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>P086</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Eselami E-ihracat (@eselamiturkiye)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/eselamiturkiye</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="5">
         <f>IF(J90="","",J90+4)</f>
@@ -10133,18 +12591,54 @@
       <c r="W90" s="13" t="n"/>
       <c r="X90" s="14" t="n"/>
       <c r="Y90" s="14" t="n"/>
-      <c r="Z90" s="8" t="n"/>
+      <c r="Z90" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-export marketplace brand. Tiny X presence.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>P087</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Kerem Başalı (@k_basali)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/k_basali</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>33144</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="5">
         <f>IF(J91="","",J91+4)</f>
@@ -10173,18 +12667,52 @@
       <c r="W91" s="13" t="n"/>
       <c r="X91" s="14" t="n"/>
       <c r="Y91" s="14" t="n"/>
-      <c r="Z91" s="8" t="n"/>
+      <c r="Z91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WAVE 2 (tool founder, contact after 2–3 wave-1 partners are signed). Shortlist 2026-10-20: WAVE 2: co-founder of Toolsy.io (Etsy SEO tool + Chrome extension; X bio + Product Hunt, checked 2026-10-20). Same handling as Konak: contact only after 2–3 wave-1 partners are signed, complementary pitch. Also owns t.me/etsyilegelir. | Etsy seller, founder of Podkon/Toolsy/Eihracatyolu. SAME OWNER </t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n"/>
-      <c r="B92" s="8" t="n"/>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>P088</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Barış Karakaya (@BarisKarakaya / @BarisKrya)</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>x_voice</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/BarisKarakaya</t>
+        </is>
+      </c>
       <c r="F92" s="12" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
+      <c r="G92" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="5">
         <f>IF(J92="","",J92+4)</f>
@@ -10213,18 +12741,54 @@
       <c r="W92" s="13" t="n"/>
       <c r="X92" s="14" t="n"/>
       <c r="Y92" s="14" t="n"/>
-      <c r="Z92" s="8" t="n"/>
+      <c r="Z92" s="8" t="inlineStr">
+        <is>
+          <t>UNVERIFIED link. Shortlist 2026-10-20: Etsy and Amazon Handmade seller who writes Etsy guides. Both handles return "user not found" on the profile API today (renamed/suspended?).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n"/>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="n"/>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>P089</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Burak Çatak</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@burakcatakecom</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>135000</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="5">
         <f>IF(J93="","",J93+4)</f>
@@ -10253,18 +12817,54 @@
       <c r="W93" s="13" t="n"/>
       <c r="X93" s="14" t="n"/>
       <c r="Y93" s="14" t="n"/>
-      <c r="Z93" s="8" t="n"/>
+      <c r="Z93" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft E4 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Etsy/POD/AI/Amazon. Etsy ornament-season videos, collab with podbul.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n"/>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="12" t="n"/>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>P090</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Milyonline (Murat Akdemir)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@milyonline</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>114000</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="5">
         <f>IF(J94="","",J94+4)</f>
@@ -10293,18 +12893,54 @@
       <c r="W94" s="13" t="n"/>
       <c r="X94" s="14" t="n"/>
       <c r="Y94" s="14" t="n"/>
-      <c r="Z94" s="8" t="n"/>
+      <c r="Z94" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Amazon consultancy (8 years). Client-result videos (e.g. 45K TL to 480K TL profit): consulting seller, watch income framing.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n"/>
-      <c r="B95" s="8" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>P091</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>URS Danışmanlık</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@ursdanismanlik</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>181000</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="5">
         <f>IF(J95="","",J95+4)</f>
@@ -10333,18 +12969,54 @@
       <c r="W95" s="13" t="n"/>
       <c r="X95" s="14" t="n"/>
       <c r="Y95" s="14" t="n"/>
-      <c r="Z95" s="8" t="n"/>
+      <c r="Z95" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Amazon/Walmart global selling training and consulting firm (COURSE/CONSULTING SELLER). Company is reachable.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n"/>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>P092</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Burak Yayla</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@burakyayla_amz</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="5">
         <f>IF(J96="","",J96+4)</f>
@@ -10373,18 +13045,54 @@
       <c r="W96" s="13" t="n"/>
       <c r="X96" s="14" t="n"/>
       <c r="Y96" s="14" t="n"/>
-      <c r="Z96" s="8" t="n"/>
+      <c r="Z96" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Amazon FBA/private label education. Some titles with $ targets ("3.000$ sermaye ile 3.000$ kâr mümkün mü?").</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n"/>
-      <c r="B97" s="8" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>P093</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>MZN Danışmanlık</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mzndanismanlik</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J97" s="5" t="n"/>
       <c r="K97" s="5">
         <f>IF(J97="","",J97+4)</f>
@@ -10413,18 +13121,54 @@
       <c r="W97" s="13" t="n"/>
       <c r="X97" s="14" t="n"/>
       <c r="Y97" s="14" t="n"/>
-      <c r="Z97" s="8" t="n"/>
+      <c r="Z97" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M7 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Says it is an official Amazon partner (training/consulting). Runs seminars. Also runs TG dropshippingmzn (5.5K).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n"/>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="n"/>
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>P094</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Tayfun Tolga Bilgi</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@tayfuntolgabilgi</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>322000</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J98" s="5" t="n"/>
       <c r="K98" s="5">
         <f>IF(J98="","",J98+4)</f>
@@ -10453,18 +13197,54 @@
       <c r="W98" s="13" t="n"/>
       <c r="X98" s="14" t="n"/>
       <c r="Y98" s="14" t="n"/>
-      <c r="Z98" s="8" t="n"/>
+      <c r="Z98" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft E3 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Amazon stoksuz e-ticaret plus Etsy digital-product experiments, documented candidly (0 TL shop first 2 weeks).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="8" t="n"/>
-      <c r="C99" s="4" t="n"/>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="4" t="n"/>
-      <c r="H99" s="4" t="n"/>
-      <c r="I99" s="4" t="n"/>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>P095</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Hakan Gerin</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@hakangerin</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>112000</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="5">
         <f>IF(J99="","",J99+4)</f>
@@ -10493,18 +13273,54 @@
       <c r="W99" s="13" t="n"/>
       <c r="X99" s="14" t="n"/>
       <c r="Y99" s="14" t="n"/>
-      <c r="Z99" s="8" t="n"/>
+      <c r="Z99" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft E2 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Etsy stoksuz (Yuppion), jewelry/metal wall art, order economics.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n"/>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="12" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>P096</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>E-Ticaret Türkiye (eCommerce Turkey)</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@eticareturkiye</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>459000</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="5">
         <f>IF(J100="","",J100+4)</f>
@@ -10533,18 +13349,54 @@
       <c r="W100" s="13" t="n"/>
       <c r="X100" s="14" t="n"/>
       <c r="Y100" s="14" t="n"/>
-      <c r="Z100" s="8" t="n"/>
+      <c r="Z100" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M6 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: E-commerce media brand running city events (Sivas, Gaziantep) with Etsy speakers. Same org as FB group eticareturkiye. Event sponsorship angle.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="n"/>
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>BAZ Girişim</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bazgirisim</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>737000</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="5">
         <f>IF(J101="","",J101+4)</f>
@@ -10573,18 +13425,52 @@
       <c r="W101" s="13" t="n"/>
       <c r="X101" s="14" t="n"/>
       <c r="Y101" s="14" t="n"/>
-      <c r="Z101" s="8" t="n"/>
+      <c r="Z101" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Export consultancy (B2B-focused) with ETGB/e-ihracat videos and government-incentive content. X @Baz_Girisim.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n"/>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>P098</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Girişim Atölyesi</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@girisimatolyesi-tr</t>
+        </is>
+      </c>
       <c r="F102" s="12" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
+      <c r="G102" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="5">
         <f>IF(J102="","",J102+4)</f>
@@ -10613,18 +13499,54 @@
       <c r="W102" s="13" t="n"/>
       <c r="X102" s="14" t="n"/>
       <c r="Y102" s="14" t="n"/>
-      <c r="Z102" s="8" t="n"/>
+      <c r="Z102" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Platform connecting TR handmade workshops to Etsy/Amazon/eBay sellers. Strong maker-to-export fit, possible integration partner. Subscriber count hidden.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n"/>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="n"/>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="4" t="n"/>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>P099</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Esra Bayram</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@esrabayramco</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>656000</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J103" s="5" t="n"/>
       <c r="K103" s="5">
         <f>IF(J103="","",J103+4)</f>
@@ -10653,18 +13575,54 @@
       <c r="W103" s="13" t="n"/>
       <c r="X103" s="14" t="n"/>
       <c r="Y103" s="14" t="n"/>
-      <c r="Z103" s="8" t="n"/>
+      <c r="Z103" s="8" t="inlineStr">
+        <is>
+          <t>DO NOT CONTACT (income-promise marketing). Shortlist 2026-10-20: Etsy POD guides (Kittl, FomaPrint). Channel framed around "para kazanma yolları / pasif gelir".</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n"/>
-      <c r="B104" s="8" t="n"/>
-      <c r="C104" s="4" t="n"/>
-      <c r="D104" s="4" t="n"/>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="12" t="n"/>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="n"/>
-      <c r="I104" s="4" t="n"/>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>P100</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Barış Digital</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@BarisDigital</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="5">
         <f>IF(J104="","",J104+4)</f>
@@ -10693,18 +13651,54 @@
       <c r="W104" s="13" t="n"/>
       <c r="X104" s="14" t="n"/>
       <c r="Y104" s="14" t="n"/>
-      <c r="Z104" s="8" t="n"/>
+      <c r="Z104" s="8" t="inlineStr">
+        <is>
+          <t>DO NOT CONTACT (income-promise marketing). Shortlist 2026-10-20: Printify/Etsy POD tutorials mixed with "app that earns you money from your phone" content.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n"/>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="4" t="n"/>
-      <c r="D105" s="4" t="n"/>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="12" t="n"/>
-      <c r="G105" s="4" t="n"/>
-      <c r="H105" s="4" t="n"/>
-      <c r="I105" s="4" t="n"/>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Okyanusi University</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@okyanusiuniversity3463</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>895000</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="5">
         <f>IF(J105="","",J105+4)</f>
@@ -10733,18 +13727,52 @@
       <c r="W105" s="13" t="n"/>
       <c r="X105" s="14" t="n"/>
       <c r="Y105" s="14" t="n"/>
-      <c r="Z105" s="8" t="n"/>
+      <c r="Z105" s="8" t="inlineStr">
+        <is>
+          <t>DO NOT CONTACT (income-promise marketing). Shortlist 2026-10-20: Akın Yılmaz brand: AI tools for online sellers, with titles like "Make $70,000 from Amazon with AI without showing your face".</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n"/>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
-      <c r="E106" s="4" t="n"/>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>P102</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Vergi Merkezi | Mali Müşavirlik (Umut Akpınar, CPA)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>https://vergimerkezi.com.tr/e-ticaret-ve-e-ihracat-icin-ihtisaslasmis-mali-musavirlik-hizmetleri/</t>
+        </is>
+      </c>
       <c r="F106" s="12" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
+      <c r="G106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J106" s="5" t="n"/>
       <c r="K106" s="5">
         <f>IF(J106="","",J106+4)</f>
@@ -10773,18 +13801,52 @@
       <c r="W106" s="13" t="n"/>
       <c r="X106" s="14" t="n"/>
       <c r="Y106" s="14" t="n"/>
-      <c r="Z106" s="8" t="n"/>
+      <c r="Z106" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M8 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Specialised in e-commerce/e-ihracat: mikro ihracat ETGB, KDV iadesi, Amazon/Etsy/Trendyol. Also YouTube @VergiMerkezi and X @Vergi_Merkezi (29 followers).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n"/>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>P103</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>İstanbul Mali Müşavirlik (SMMM Ayşe Nil Boyacıoğlu)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.istanbulmalimusavirlik.net/etsy-amazon-ihracat-muhasebesi/</t>
+        </is>
+      </c>
       <c r="F107" s="12" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
+      <c r="G107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J107" s="5" t="n"/>
       <c r="K107" s="5">
         <f>IF(J107="","",J107+4)</f>
@@ -10813,18 +13875,52 @@
       <c r="W107" s="13" t="n"/>
       <c r="X107" s="14" t="n"/>
       <c r="Y107" s="14" t="n"/>
-      <c r="Z107" s="8" t="n"/>
+      <c r="Z107" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M9 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Dedicated Etsy/Amazon FBA e-ihracat tax and company-setup guide. LinkedIn company page public.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n"/>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>P104</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>SMMM Sinem Yavuz</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>https://sinemyavuz.com.tr/blog/e-ticaret-pazaryeri-vergilendirme</t>
+        </is>
+      </c>
       <c r="F108" s="12" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
-      <c r="I108" s="4" t="n"/>
+      <c r="G108" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="5">
         <f>IF(J108="","",J108+4)</f>
@@ -10853,18 +13949,52 @@
       <c r="W108" s="13" t="n"/>
       <c r="X108" s="14" t="n"/>
       <c r="Y108" s="14" t="n"/>
-      <c r="Z108" s="8" t="n"/>
+      <c r="Z108" s="8" t="inlineStr">
+        <is>
+          <t>WAVE 1 · draft M10 in docs/gtm/partners/wave1_first_messages.md. Shortlist 2026-10-20: Tax/accounting for Trendyol, HB, Etsy, Amazon and Shopier sellers. Public Instagram/LinkedIn/Medium.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n"/>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>P105</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>SMMM Hakan Yılmaz</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hakanyilmaz.tr/amazon-etsy-gibi-platformlar-uzerinden-dropshipping-vergilendirmesi/</t>
+        </is>
+      </c>
       <c r="F109" s="12" t="n"/>
-      <c r="G109" s="4" t="n"/>
-      <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="n"/>
+      <c r="G109" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="5">
         <f>IF(J109="","",J109+4)</f>
@@ -10893,18 +14023,52 @@
       <c r="W109" s="13" t="n"/>
       <c r="X109" s="14" t="n"/>
       <c r="Y109" s="14" t="n"/>
-      <c r="Z109" s="8" t="n"/>
+      <c r="Z109" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Content on Etsy/Amazon dropshipping taxation for TR residents. Public social links on site.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="n"/>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>P106</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>SMMM Serhat Aydın</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aydinserhat.com.tr/e-ticaret-muhasebesi</t>
+        </is>
+      </c>
       <c r="F110" s="12" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
+      <c r="G110" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="5">
         <f>IF(J110="","",J110+4)</f>
@@ -10933,18 +14097,54 @@
       <c r="W110" s="13" t="n"/>
       <c r="X110" s="14" t="n"/>
       <c r="Y110" s="14" t="n"/>
-      <c r="Z110" s="8" t="n"/>
+      <c r="Z110" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-commerce accounting for Trendyol/HB/Amazon/Etsy sellers. LinkedIn public.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n"/>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="4" t="n"/>
-      <c r="H111" s="4" t="n"/>
-      <c r="I111" s="4" t="n"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>P107</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Cemil Kır, İSMMMO Mali Müşavir (@CemilCPA)</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/CemilCPA</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>9710</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="5">
         <f>IF(J111="","",J111+4)</f>
@@ -10973,18 +14173,54 @@
       <c r="W111" s="13" t="n"/>
       <c r="X111" s="14" t="n"/>
       <c r="Y111" s="14" t="n"/>
-      <c r="Z111" s="8" t="n"/>
+      <c r="Z111" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Mali müşavir active on X (13.9K tweets). Posted the 2026 micro-export limit change for e-commerce sellers.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="n"/>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="12" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>P108</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Mehmet Akif Birkan (@makifbirkan)</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/makifbirkan</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>3681</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="5">
         <f>IF(J112="","",J112+4)</f>
@@ -11013,18 +14249,54 @@
       <c r="W112" s="13" t="n"/>
       <c r="X112" s="14" t="n"/>
       <c r="Y112" s="14" t="n"/>
-      <c r="Z112" s="8" t="n"/>
+      <c r="Z112" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-ihracat consultant and trainer: US/UK/EU company setup, accounting and tax. COURSE/CONSULTING SELLER.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n"/>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>P109</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Murat Oktay, Nokta Muhasebe (@Murat__OKTAY)</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/Murat__OKTAY</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>2892</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="5">
         <f>IF(J113="","",J113+4)</f>
@@ -11053,18 +14325,54 @@
       <c r="W113" s="13" t="n"/>
       <c r="X113" s="14" t="n"/>
       <c r="Y113" s="14" t="n"/>
-      <c r="Z113" s="8" t="n"/>
+      <c r="Z113" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Mali müşavirlik firm owner. Posts mikro ihracat/ETGB rule changes.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="n"/>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="12" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="n"/>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>P110</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Becommer.com (@Becommercom)</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/becommercom</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="5">
         <f>IF(J114="","",J114+4)</f>
@@ -11093,18 +14401,54 @@
       <c r="W114" s="13" t="n"/>
       <c r="X114" s="14" t="n"/>
       <c r="Y114" s="14" t="n"/>
-      <c r="Z114" s="8" t="n"/>
+      <c r="Z114" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: E-ihracat plus Amazon/Etsy consultancy, logistics, foreign company setup, trademark. Small social reach, but a service firm that could refer clients.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n"/>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="4" t="n"/>
-      <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="4" t="n"/>
-      <c r="H115" s="4" t="n"/>
-      <c r="I115" s="4" t="n"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>P111</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>B2CDirect (@B2CDirect)</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>musavir</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/b2cdirect</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="5">
         <f>IF(J115="","",J115+4)</f>
@@ -11133,7 +14477,11 @@
       <c r="W115" s="13" t="n"/>
       <c r="X115" s="14" t="n"/>
       <c r="Y115" s="14" t="n"/>
-      <c r="Z115" s="8" t="n"/>
+      <c r="Z115" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist 2026-10-20: Calls itself "Türkiye'nin E-İhracat Uzmanı" (co-founder Yusuf İbili runs e-export trainings). Small X reach.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -29344,7 +32692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29530,12 +32878,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Outreach messages (Varyant 1–4 + follow-ups)</t>
+          <t>Partner pack: README + after-yes checklist</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/outreach-messages.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/README.md</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -29543,11 +32891,7 @@
           <t>Merisa, Ekin</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Partner Varyant 5/6 are in gameplan §4.5</t>
-        </is>
-      </c>
+      <c r="E10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -29557,12 +32901,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Social kit + claims cheat sheet</t>
+          <t>Wave-1 first messages (15 drafts + status)</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/README.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/wave1_first_messages.md</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -29570,7 +32914,11 @@
           <t>Merisa, Ekin</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>M1–M10 Merisa, E1–E5 Ekin</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -29580,24 +32928,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>30-day social calendar</t>
+          <t>Partner terms (Turkish, send as PDF)</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/ortaklik-sartlari.md</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Ekin</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Phase 2 Instagram</t>
-        </is>
-      </c>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -29607,24 +32951,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ads playbook</t>
+          <t>Partner FAQ (Turkish answers)</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/ads-playbook.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/ortak-sss.md</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Phase 2 only</t>
-        </is>
-      </c>
+          <t>Merisa, Ekin</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -29634,12 +32974,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Legal notes (İYS, #işbirliği, KVKK)</t>
+          <t>Live demo script (30 min)</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/canli-demo-senaryosu.md</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -29657,12 +32997,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Communities list</t>
+          <t>Shortlist wave 1 (89 rows, also in Partner pipeline)</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/communities.csv</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/partners/shortlist-wave1.csv</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -29680,113 +33020,121 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Blog content calendar</t>
+          <t>Outreach messages (Varyant 1–4 + follow-ups)</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/outreach-messages.md</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
+          <t>Merisa, Ekin</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Partner Varyant 5/6 are in gameplan §4.5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Admin: partners report</t>
+          <t>Social kit + claims cheat sheet</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/admin/partners</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/README.md</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Atilla, Merisa (admin role)</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Signups / activated / paying per partner</t>
-        </is>
-      </c>
+          <t>Merisa, Ekin</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Partner dashboard (after Stage B)</t>
+          <t>30-day social calendar</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/app/ortaklik</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/calendar-30d.md</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>Ekin</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2 Instagram</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Pricing page</t>
+          <t>Ads playbook</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/fiyatlandirma</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/ads-playbook.md</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Everyone</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2 only</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Legal notes (İYS, #işbirliği, KVKK)</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/login?mode=signup</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/legal-notes.md</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Merisa, Ekin</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -29794,17 +33142,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Use-case pages (ad/partner landing)</t>
+          <t>Communities list</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/cozumler</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/social/communities.csv</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -29812,31 +33160,27 @@
           <t>Merisa, Ekin</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>etsy-satici, ebay-satici, ai-ilan-optimizasyonu, mikro-ihracat-kargo-etgb, trendyoldan-dunyaya, urun-arastirma-arbitraj</t>
-        </is>
-      </c>
+      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Templates</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>How-to guides</t>
+          <t>Blog content calendar</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/nasil-kullanirim</t>
+          <t>https://github.com/bloodyteeths/kolayxport_supa/blob/main/docs/gtm/seo/content-calendar.md</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Merisa</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
@@ -29849,40 +33193,44 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Health check</t>
+          <t>Admin: partners report</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>https://kolayxport.com/api/health</t>
+          <t>https://kolayxport.com/admin/partners</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
+          <t>Atilla, Merisa (admin role)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Signups / activated / paying per partner</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chrome extension (Web Store)</t>
+          <t>Partner dashboard (after Stage B)</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>https://chromewebstore.google.com/detail/fjlfihofjojemlofkfejikgdbjemncba</t>
+          <t>https://kolayxport.com/app/ortaklik</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Partners</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -29890,22 +33238,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Extension promo video</t>
+          <t>Pricing page</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>https://youtu.be/RtHJlVkvAqg</t>
+          <t>https://kolayxport.com/fiyatlandirma</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Merisa, Ekin</t>
+          <t>Everyone</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -29913,76 +33261,72 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Google Tag Manager (GTM-N6SW5T7K)</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>https://tagmanager.google.com/?authuser=kolayxport@gmail.com#/container/accounts/6383523253/containers/267664935/workspaces/2</t>
+          <t>https://kolayxport.com/login?mode=signup</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Atilla, Merisa</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Account KolayXport (Tamsar, Inc.) on kolayxport@gmail.com; v2 published 19 Oct</t>
-        </is>
-      </c>
+          <t>Everyone</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Google Analytics 4 (G-V4ZC6HS65N)</t>
+          <t>Use-case pages (ad/partner landing)</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>https://analytics.google.com/analytics/web/?authuser=kolayxport@gmail.com#/a412601386p559673981/reports/intelligenthome</t>
+          <t>https://kolayxport.com/cozumler</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Atilla, Merisa</t>
+          <t>Merisa, Ekin</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Property kolayxport.com, Türkiye time zone; Merisa needs viewer access</t>
+          <t>etsy-satici, ebay-satici, ai-ilan-optimizasyonu, mikro-ihracat-kargo-etgb, trendyoldan-dunyaya, urun-arastirma-arbitraj</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>YouTube Studio</t>
+          <t>How-to guides</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com</t>
+          <t>https://kolayxport.com/nasil-kullanirim</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Atilla</t>
+          <t>Everyone</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -29990,17 +33334,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Stripe dashboard (Tamsar, Inc.)</t>
+          <t>Health check</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com</t>
+          <t>https://kolayxport.com/api/health</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -30008,11 +33352,7 @@
           <t>Atilla</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Coupons, promo codes, Global Payouts</t>
-        </is>
-      </c>
+      <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -30022,17 +33362,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Reklam Kurulu influencer guide (send to partners)</t>
+          <t>Chrome extension (Web Store)</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>https://ticaret.gov.tr/haberler/ticaret-bakanligi-sosyal-medya-etkileyicileri-icin-kilavuz-yayimladi</t>
+          <t>https://chromewebstore.google.com/detail/fjlfihofjojemlofkfejikgdbjemncba</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Merisa, Ekin</t>
+          <t>Everyone</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -30045,17 +33385,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Bionluk (freelancers)</t>
+          <t>Extension promo video</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>https://bionluk.com</t>
+          <t>https://youtu.be/RtHJlVkvAqg</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Merisa</t>
+          <t>Merisa, Ekin</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
@@ -30068,66 +33408,174 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
+          <t>Google Tag Manager (GTM-N6SW5T7K)</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>https://tagmanager.google.com/?authuser=kolayxport@gmail.com#/container/accounts/6383523253/containers/267664935/workspaces/2</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Atilla, Merisa</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Account KolayXport (Tamsar, Inc.) on kolayxport@gmail.com; v2 published 19 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Google Analytics 4 (G-V4ZC6HS65N)</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>https://analytics.google.com/analytics/web/?authuser=kolayxport@gmail.com#/a412601386p559673981/reports/intelligenthome</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Atilla, Merisa</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Property kolayxport.com, Türkiye time zone; Merisa needs viewer access</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>YouTube Studio</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Stripe dashboard (Tamsar, Inc.)</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>https://dashboard.stripe.com</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Coupons, promo codes, Global Payouts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Reklam Kurulu influencer guide (send to partners)</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>https://ticaret.gov.tr/haberler/ticaret-bakanligi-sosyal-medya-etkileyicileri-icin-kilavuz-yayimladi</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Merisa, Ekin</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Bionluk (freelancers)</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>https://bionluk.com</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Merisa</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>PraPazar packages (pricing reference)</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>https://prapazar.com/tr/paketler</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Atilla</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Checked 2026-10-19</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -30303,6 +33751,48 @@
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n"/>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="8" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30334,6 +33824,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30345,7 +33841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30837,49 +34333,95 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Tool founders go to wave 2: Ahmet Konak (Optimsy) and Kerem Başalı (Toolsy.io) are contacted only after 2–3 wave-1 partners are signed, with a complementary pitch (orders, finance, stock), not listing SEO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Orchestrator for Atilla</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>orchestrator 2026-10-20</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Wave-1 first messages: 15 drafts, Merisa 10 / Ekin 5 (matching hours), no prices, no links, partner-first</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Orchestrator for Atilla</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>docs/gtm/partners/wave1_first_messages.md</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>CHECK BEFORE CLAIM: every status claim cites its primary source + timestamp, or says 'unverified'</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Atilla</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>orchestrator 2026-10-20</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Daily spot-check ~19:15 Skopje</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
         <v>46314</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Tracking accounts created under kolayxport@gmail.com: GTM container GTM-N6SW5T7K (account KolayXport (Tamsar, Inc.)) and GA4 property G-V4ZC6HS65N; GTM v2 published with GA4 base + funnel-event tags</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Atilla (asked Claude to do it)</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>this session</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Google data-sharing options left off</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -31216,6 +34758,27 @@
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
